--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
@@ -4258,7 +4258,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
@@ -4258,7 +4258,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
@@ -5010,7 +5010,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
@@ -7076,7 +7076,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
@@ -7076,7 +7076,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
@@ -4258,7 +4258,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
@@ -4258,7 +4258,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
@@ -4258,7 +4258,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
@@ -4258,7 +4258,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
@@ -4258,7 +4258,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
@@ -4258,7 +4258,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251029_201937.xlsx
@@ -4258,7 +4258,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
